--- a/r5-core-76-add-healthcare-service/StructureDefinition-at-core-practitioner.xlsx
+++ b/r5-core-76-add-healthcare-service/StructureDefinition-at-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3372" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3375" uniqueCount="463">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T21:36:48+00:00</t>
+    <t>2026-10-11T20:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -747,6 +747,12 @@
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.type</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|5.0.0</t>
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.system</t>
@@ -1233,6 +1239,10 @@
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
   </si>
   <si>
     <t>ORC-24, STF-11, ROL-11, PRT-14</t>
@@ -1789,7 +1799,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="46.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -4571,9 +4581,11 @@
       <c r="X24" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y24" s="2"/>
+      <c r="Y24" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4623,7 +4635,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>192</v>
@@ -4652,7 +4664,7 @@
         <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>194</v>
@@ -4668,7 +4680,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>21</v>
@@ -4742,7 +4754,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>202</v>
@@ -4771,7 +4783,7 @@
         <v>203</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>205</v>
@@ -4859,7 +4871,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>213</v>
@@ -4974,7 +4986,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>221</v>
@@ -5091,10 +5103,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5206,10 +5218,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5323,10 +5335,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5352,13 +5364,13 @@
         <v>203</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5408,7 +5420,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5417,7 +5429,7 @@
         <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
@@ -5440,10 +5452,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5469,13 +5481,13 @@
         <v>105</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5504,10 +5516,10 @@
         <v>188</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5525,7 +5537,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5557,10 +5569,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5586,13 +5598,13 @@
         <v>151</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5642,7 +5654,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5651,7 +5663,7 @@
         <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>103</v>
@@ -5663,7 +5675,7 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
@@ -5674,10 +5686,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5703,13 +5715,13 @@
         <v>203</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5717,7 +5729,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>21</v>
@@ -5759,7 +5771,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5768,7 +5780,7 @@
         <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>103</v>
@@ -5791,13 +5803,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>150</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>21</v>
@@ -5910,7 +5922,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>162</v>
@@ -6025,7 +6037,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>168</v>
@@ -6142,7 +6154,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>173</v>
@@ -6261,7 +6273,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>182</v>
@@ -6326,9 +6338,11 @@
       <c r="X39" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y39" s="2"/>
+      <c r="Y39" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6378,7 +6392,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>192</v>
@@ -6407,7 +6421,7 @@
         <v>105</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M40" t="s" s="2">
         <v>194</v>
@@ -6423,7 +6437,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>21</v>
@@ -6497,7 +6511,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>202</v>
@@ -6614,7 +6628,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>213</v>
@@ -6729,7 +6743,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>221</v>
@@ -6846,10 +6860,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6961,10 +6975,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7078,10 +7092,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7107,13 +7121,13 @@
         <v>203</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7163,7 +7177,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7172,7 +7186,7 @@
         <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>103</v>
@@ -7195,10 +7209,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7224,13 +7238,13 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7259,10 +7273,10 @@
         <v>188</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7280,7 +7294,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7312,10 +7326,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7341,13 +7355,13 @@
         <v>151</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7397,7 +7411,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7406,7 +7420,7 @@
         <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>103</v>
@@ -7418,7 +7432,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7429,10 +7443,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7458,13 +7472,13 @@
         <v>203</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7472,7 +7486,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>21</v>
@@ -7514,7 +7528,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7523,7 +7537,7 @@
         <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>103</v>
@@ -7546,13 +7560,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>150</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>21</v>
@@ -7665,7 +7679,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>162</v>
@@ -7780,7 +7794,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>168</v>
@@ -7897,7 +7911,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>173</v>
@@ -8016,7 +8030,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>182</v>
@@ -8081,9 +8095,11 @@
       <c r="X54" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y54" s="2"/>
+      <c r="Y54" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8133,7 +8149,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>192</v>
@@ -8162,7 +8178,7 @@
         <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>194</v>
@@ -8178,7 +8194,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>21</v>
@@ -8252,7 +8268,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>202</v>
@@ -8369,7 +8385,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>213</v>
@@ -8484,7 +8500,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>221</v>
@@ -8601,10 +8617,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8716,10 +8732,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8833,10 +8849,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8862,13 +8878,13 @@
         <v>203</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8918,7 +8934,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8927,7 +8943,7 @@
         <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>103</v>
@@ -8950,10 +8966,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8979,13 +8995,13 @@
         <v>105</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9014,10 +9030,10 @@
         <v>188</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -9035,7 +9051,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9067,10 +9083,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9096,13 +9112,13 @@
         <v>151</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9152,7 +9168,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9161,7 +9177,7 @@
         <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>103</v>
@@ -9173,7 +9189,7 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -9184,10 +9200,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9213,13 +9229,13 @@
         <v>203</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9227,7 +9243,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>21</v>
@@ -9269,7 +9285,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9278,7 +9294,7 @@
         <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>103</v>
@@ -9301,10 +9317,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9327,70 +9343,70 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q65" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="R65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9405,16 +9421,16 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>21</v>
@@ -9422,10 +9438,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9448,19 +9464,19 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9509,7 +9525,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9527,24 +9543,24 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9567,19 +9583,19 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9628,7 +9644,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9646,24 +9662,24 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9689,14 +9705,14 @@
         <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9724,10 +9740,10 @@
         <v>115</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>21</v>
@@ -9745,7 +9761,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9763,24 +9779,24 @@
         <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9806,10 +9822,10 @@
         <v>203</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9892,10 +9908,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9921,10 +9937,10 @@
         <v>139</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10005,13 +10021,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>21</v>
@@ -10033,13 +10049,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10122,10 +10138,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10151,10 +10167,10 @@
         <v>111</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10205,7 +10221,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10237,10 +10253,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10263,17 +10279,17 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10322,7 +10338,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10340,24 +10356,24 @@
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10380,16 +10396,16 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10439,7 +10455,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10460,7 +10476,7 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10471,10 +10487,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10497,19 +10513,19 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10558,7 +10574,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10570,30 +10586,30 @@
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>103</v>
+        <v>392</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10616,17 +10632,17 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10675,7 +10691,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10696,21 +10712,21 @@
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10733,16 +10749,16 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10792,7 +10808,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10810,24 +10826,24 @@
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10939,10 +10955,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11056,14 +11072,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11085,10 +11101,10 @@
         <v>139</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>142</v>
@@ -11143,7 +11159,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11175,10 +11191,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11204,14 +11220,14 @@
         <v>151</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -11260,7 +11276,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11281,7 +11297,7 @@
         <v>21</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -11292,10 +11308,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11321,10 +11337,10 @@
         <v>183</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11351,31 +11367,31 @@
         <v>21</v>
       </c>
       <c r="X82" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>91</v>
@@ -11396,21 +11412,21 @@
         <v>21</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11436,14 +11452,14 @@
         <v>214</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -11492,7 +11508,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11513,21 +11529,21 @@
         <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11553,10 +11569,10 @@
         <v>222</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11607,7 +11623,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11628,7 +11644,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -11639,10 +11655,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11665,16 +11681,16 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11724,7 +11740,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11745,7 +11761,7 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -11756,10 +11772,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11871,10 +11887,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11988,14 +12004,14 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12017,10 +12033,10 @@
         <v>139</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>142</v>
@@ -12075,7 +12091,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12107,10 +12123,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12136,16 +12152,16 @@
         <v>183</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>21</v>
@@ -12194,7 +12210,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>91</v>
@@ -12212,10 +12228,10 @@
         <v>21</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
@@ -12226,10 +12242,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12252,19 +12268,19 @@
         <v>21</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -12313,7 +12329,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12334,7 +12350,7 @@
         <v>21</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>

--- a/r5-core-76-add-healthcare-service/StructureDefinition-at-core-practitioner.xlsx
+++ b/r5-core-76-add-healthcare-service/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T20:03:30+00:00</t>
+    <t>2026-10-12T11:43:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
